--- a/Diarias/Diarias.xlsx
+++ b/Diarias/Diarias.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\henrique.santos\orcamento2027\budgetflow-insights\Diarias\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BFF725E9-18F8-4709-AE96-A25B4584A21F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08EE3ADC-8BB0-465D-9938-85F59382B2E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{202230F5-B999-493F-8126-8B87BE85ADD7}"/>
   </bookViews>
@@ -51,7 +51,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -62,6 +62,12 @@
     <font>
       <b/>
       <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color rgb="FF1E293B"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
@@ -107,13 +113,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="17" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="3" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="4" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -542,7 +550,9 @@
       <c r="B3" s="1">
         <v>12.569965922191114</v>
       </c>
-      <c r="C3" s="1"/>
+      <c r="C3" s="1">
+        <v>10.331561602390099</v>
+      </c>
       <c r="D3" s="1"/>
       <c r="E3" s="1"/>
       <c r="F3" s="1"/>
@@ -559,6 +569,13 @@
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.3">
       <c r="C5" s="1"/>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="F7" s="4"/>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="D9" s="4"/>
+      <c r="F9" s="5"/>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B16" s="1"/>

--- a/Diarias/Diarias.xlsx
+++ b/Diarias/Diarias.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\henrique.santos\orcamento2027\budgetflow-insights\Diarias\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08EE3ADC-8BB0-465D-9938-85F59382B2E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A552505-B268-4D24-B120-F78AC682DA0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{202230F5-B999-493F-8126-8B87BE85ADD7}"/>
   </bookViews>
@@ -51,7 +51,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -62,12 +62,6 @@
     <font>
       <b/>
       <sz val="10"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="8"/>
-      <color rgb="FF1E293B"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
@@ -113,15 +107,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="17" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="3" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="4" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -456,7 +448,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{12069B8F-9389-422B-815C-AE264BF4E6DD}">
-  <dimension ref="A1:M16"/>
+  <dimension ref="A1:M17"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="4" width="11.6640625" bestFit="1" customWidth="1"/>
@@ -553,8 +545,12 @@
       <c r="C3" s="1">
         <v>10.331561602390099</v>
       </c>
-      <c r="D3" s="1"/>
-      <c r="E3" s="1"/>
+      <c r="D3" s="1">
+        <v>16.150019197484216</v>
+      </c>
+      <c r="E3" s="1">
+        <v>9.3885126271552579</v>
+      </c>
       <c r="F3" s="1"/>
       <c r="G3" s="1"/>
       <c r="H3" s="1"/>
@@ -568,14 +564,125 @@
       <c r="C4" s="3"/>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="B5" s="1"/>
       <c r="C5" s="1"/>
+      <c r="D5" s="1"/>
+      <c r="E5" s="1"/>
+      <c r="F5" s="1"/>
+      <c r="G5" s="1"/>
+      <c r="H5" s="1"/>
+      <c r="I5" s="1"/>
+      <c r="J5" s="1"/>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="B6" s="1"/>
+      <c r="C6" s="1"/>
+      <c r="D6" s="1"/>
+      <c r="E6" s="1"/>
+      <c r="F6" s="1"/>
+      <c r="G6" s="1"/>
+      <c r="H6" s="1"/>
+      <c r="I6" s="1"/>
+      <c r="J6" s="1"/>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="F7" s="4"/>
+      <c r="B7" s="1"/>
+      <c r="C7" s="1"/>
+      <c r="D7" s="1"/>
+      <c r="E7" s="1"/>
+      <c r="F7" s="1"/>
+      <c r="G7" s="1"/>
+      <c r="H7" s="1"/>
+      <c r="I7" s="1"/>
+      <c r="J7" s="1"/>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="B8" s="1"/>
+      <c r="C8" s="1"/>
+      <c r="D8" s="1"/>
+      <c r="E8" s="1"/>
+      <c r="F8" s="1"/>
+      <c r="G8" s="1"/>
+      <c r="H8" s="1"/>
+      <c r="I8" s="1"/>
+      <c r="J8" s="1"/>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="D9" s="4"/>
-      <c r="F9" s="5"/>
+      <c r="B9" s="1"/>
+      <c r="C9" s="1"/>
+      <c r="D9" s="1"/>
+      <c r="E9" s="1"/>
+      <c r="F9" s="1"/>
+      <c r="G9" s="1"/>
+      <c r="H9" s="1"/>
+      <c r="I9" s="1"/>
+      <c r="J9" s="1"/>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="B10" s="1"/>
+      <c r="C10" s="1"/>
+      <c r="D10" s="1"/>
+      <c r="E10" s="1"/>
+      <c r="F10" s="1"/>
+      <c r="G10" s="1"/>
+      <c r="H10" s="1"/>
+      <c r="I10" s="1"/>
+      <c r="J10" s="1"/>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="B11" s="1"/>
+      <c r="C11" s="1"/>
+      <c r="D11" s="1"/>
+      <c r="E11" s="1"/>
+      <c r="F11" s="1"/>
+      <c r="G11" s="1"/>
+      <c r="H11" s="1"/>
+      <c r="I11" s="1"/>
+      <c r="J11" s="1"/>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="B12" s="1"/>
+      <c r="C12" s="1"/>
+      <c r="D12" s="1"/>
+      <c r="E12" s="1"/>
+      <c r="F12" s="1"/>
+      <c r="G12" s="1"/>
+      <c r="H12" s="1"/>
+      <c r="I12" s="1"/>
+      <c r="J12" s="1"/>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="B13" s="1"/>
+      <c r="C13" s="1"/>
+      <c r="D13" s="1"/>
+      <c r="E13" s="1"/>
+      <c r="F13" s="1"/>
+      <c r="G13" s="1"/>
+      <c r="H13" s="1"/>
+      <c r="I13" s="1"/>
+      <c r="J13" s="1"/>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="B14" s="1"/>
+      <c r="C14" s="1"/>
+      <c r="D14" s="1"/>
+      <c r="E14" s="1"/>
+      <c r="F14" s="1"/>
+      <c r="G14" s="1"/>
+      <c r="H14" s="1"/>
+      <c r="I14" s="1"/>
+      <c r="J14" s="1"/>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="B15" s="1"/>
+      <c r="C15" s="1"/>
+      <c r="D15" s="1"/>
+      <c r="E15" s="1"/>
+      <c r="F15" s="1"/>
+      <c r="G15" s="1"/>
+      <c r="H15" s="1"/>
+      <c r="I15" s="1"/>
+      <c r="J15" s="1"/>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B16" s="1"/>
@@ -591,6 +698,17 @@
       <c r="L16" s="1"/>
       <c r="M16" s="1"/>
     </row>
+    <row r="17" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B17" s="1"/>
+      <c r="C17" s="1"/>
+      <c r="D17" s="1"/>
+      <c r="E17" s="1"/>
+      <c r="F17" s="1"/>
+      <c r="G17" s="1"/>
+      <c r="H17" s="1"/>
+      <c r="I17" s="1"/>
+      <c r="J17" s="1"/>
+    </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
